--- a/data/trans_orig/Q20C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización</t>
+          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,08</t>
+          <t>2,96; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 11,98</t>
+          <t>2,18; 12,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,77</t>
+          <t>5,36; 13,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 27,39</t>
+          <t>1,33; 26,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,23</t>
+          <t>3,22; 8,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,53</t>
+          <t>3,57; 9,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 19,86</t>
+          <t>4,21; 18,42</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,28</t>
+          <t>0,6; 5,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 17,45</t>
+          <t>2,4; 16,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 25,06</t>
+          <t>3,51; 25,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,32</t>
+          <t>2,16; 16,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,4</t>
+          <t>2,82; 8,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,35</t>
+          <t>2,45; 6,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,97</t>
+          <t>1,95; 6,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 28,19</t>
+          <t>2,23; 29,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,82</t>
+          <t>2,41; 7,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,79</t>
+          <t>3,24; 8,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 16,41</t>
+          <t>3,55; 16,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 16,18</t>
+          <t>2,8; 15,1</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,2</t>
+          <t>0,8; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 19,21</t>
+          <t>3,78; 18,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,45</t>
+          <t>2,0; 4,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 17,32</t>
+          <t>4,59; 18,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,08</t>
+          <t>2,83; 11,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,09</t>
+          <t>1,93; 4,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,44</t>
+          <t>3,79; 15,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,26</t>
+          <t>4,07; 14,19</t>
         </is>
       </c>
     </row>
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,11</t>
+          <t>4,51; 9,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,96</t>
+          <t>3,72; 11,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,02</t>
+          <t>0,99; 5,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,96</t>
+          <t>2,48; 9,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,46</t>
+          <t>2,98; 10,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,9</t>
+          <t>1,25; 6,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,02</t>
+          <t>0,99; 5,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,3</t>
+          <t>3,12; 7,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,54</t>
+          <t>3,89; 8,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,08</t>
+          <t>3,52; 9,19</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,99</t>
+          <t>1,93; 7,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 15,2</t>
+          <t>1,16; 15,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 30,0</t>
+          <t>2,84; 24,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,39</t>
+          <t>2,39; 6,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,0</t>
+          <t>2,0; 10,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,3</t>
+          <t>2,58; 6,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,52</t>
+          <t>2,57; 13,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 21,74</t>
+          <t>4,09; 21,21</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 18,93</t>
+          <t>1,51; 24,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,38</t>
+          <t>1,8; 5,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 28,15</t>
+          <t>7,81; 29,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,77</t>
+          <t>1,44; 5,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,2</t>
+          <t>1,5; 5,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 15,26</t>
+          <t>4,24; 15,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 13,5</t>
+          <t>2,01; 11,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 13,18</t>
+          <t>1,21; 13,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,78</t>
+          <t>1,95; 4,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 22,95</t>
+          <t>7,55; 22,2</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 24,52</t>
+          <t>7,33; 23,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 16,96</t>
+          <t>5,13; 17,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 41,52</t>
+          <t>4,83; 44,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,01</t>
+          <t>2,55; 9,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,82</t>
+          <t>2,77; 5,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,52</t>
+          <t>4,63; 11,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,54</t>
+          <t>4,3; 8,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,19</t>
+          <t>3,88; 8,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,75</t>
+          <t>5,16; 13,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 11,56</t>
+          <t>5,7; 11,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 26,63</t>
+          <t>5,85; 25,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,49</t>
+          <t>3,75; 7,57</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 16,75</t>
+          <t>2,02; 16,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 12,96</t>
+          <t>1,55; 12,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 12,85</t>
+          <t>3,7; 12,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,82</t>
+          <t>1,48; 5,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,87</t>
+          <t>3,7; 14,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,87</t>
+          <t>4,47; 11,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,21</t>
+          <t>4,21; 16,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,11</t>
+          <t>1,22; 4,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,07</t>
+          <t>3,82; 11,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,27</t>
+          <t>4,19; 10,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,46</t>
+          <t>4,49; 11,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,78</t>
+          <t>1,9; 4,79</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,93</t>
+          <t>4,97; 11,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,47</t>
+          <t>4,05; 7,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,64</t>
+          <t>5,52; 13,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,62</t>
+          <t>5,24; 10,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,43; 5,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,96</t>
+          <t>4,43; 6,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,18</t>
+          <t>4,89; 7,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,23</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,61</t>
+          <t>4,39; 7,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,76</t>
+          <t>4,52; 6,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,91</t>
+          <t>5,83; 10,25</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,54</t>
+          <t>5,18; 8,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Provincia-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,14</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,27</t>
+          <t>2,83; 7,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,07</t>
+          <t>2,05; 12,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 13,53</t>
+          <t>5,03; 12,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 26,84</t>
+          <t>1,34; 24,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,23</t>
+          <t>3,19; 8,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,69</t>
+          <t>3,63; 9,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 18,42</t>
+          <t>3,45; 18,17</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,31</t>
+          <t>0,79; 5,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 16,78</t>
+          <t>2,47; 15,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 25,06</t>
+          <t>3,51; 25,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 16,25</t>
+          <t>2,65; 16,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,23</t>
+          <t>2,94; 8,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,35</t>
+          <t>2,49; 6,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,03</t>
+          <t>2,15; 5,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 29,48</t>
+          <t>2,25; 30,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,01</t>
+          <t>2,67; 7,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,93</t>
+          <t>3,24; 9,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 16,16</t>
+          <t>3,67; 16,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,1</t>
+          <t>3,53; 14,73</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>6,76</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,9</t>
+          <t>0,8; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 18,99</t>
+          <t>3,77; 26,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,34</t>
+          <t>1,99; 4,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 18,35</t>
+          <t>3,97; 17,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 11,67</t>
+          <t>2,73; 10,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,06</t>
+          <t>1,92; 4,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 15,51</t>
+          <t>3,92; 15,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 14,19</t>
+          <t>4,03; 14,71</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>9,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>7,6</t>
         </is>
       </c>
     </row>
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,42</t>
+          <t>4,52; 9,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,5</t>
+          <t>4,72; 17,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,08</t>
+          <t>1,03; 5,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,51</t>
+          <t>2,44; 9,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,98</t>
+          <t>2,94; 10,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,83</t>
+          <t>1,59; 6,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,08</t>
+          <t>1,03; 5,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,31</t>
+          <t>3,19; 7,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,74</t>
+          <t>3,73; 8,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,19</t>
+          <t>4,33; 13,38</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>10,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>9,15</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,98</t>
+          <t>1,92; 7,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 15,2</t>
+          <t>0,96; 15,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 24,44</t>
+          <t>2,96; 24,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,73</t>
+          <t>2,39; 6,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,01</t>
+          <t>2,0; 12,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,39</t>
+          <t>2,62; 6,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,15</t>
+          <t>2,89; 14,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 21,21</t>
+          <t>4,12; 21,61</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,06</t>
+          <t>11,86</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 24,0</t>
+          <t>1,51; 18,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,52 +1426,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,37</t>
+          <t>1,8; 5,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 29,54</t>
+          <t>7,78; 27,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,03</t>
+          <t>1,44; 5,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,58</t>
+          <t>1,98; 7,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,06</t>
+          <t>1,52; 5,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 15,75</t>
+          <t>4,26; 16,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,86</t>
+          <t>2,02; 13,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,04</t>
+          <t>1,33; 13,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,71</t>
+          <t>1,99; 4,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 22,2</t>
+          <t>7,31; 22,13</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,2</t>
+          <t>5,68</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 23,82</t>
+          <t>7,0; 23,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,12</t>
+          <t>5,12; 17,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 44,52</t>
+          <t>4,87; 55,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,44</t>
+          <t>2,63; 8,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,86</t>
+          <t>2,67; 5,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,78</t>
+          <t>4,77; 11,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,31</t>
+          <t>4,33; 8,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,58</t>
+          <t>4,08; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,81</t>
+          <t>5,02; 14,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,65</t>
+          <t>5,74; 11,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 25,36</t>
+          <t>5,79; 27,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,57</t>
+          <t>4,13; 7,91</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 16,75</t>
+          <t>1,88; 15,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,9</t>
+          <t>1,42; 11,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,05</t>
+          <t>3,69; 12,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,61</t>
+          <t>1,61; 5,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 14,15</t>
+          <t>3,52; 14,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,81</t>
+          <t>4,58; 11,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,42</t>
+          <t>4,09; 15,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,22</t>
+          <t>1,38; 4,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,45</t>
+          <t>3,95; 11,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,38</t>
+          <t>4,1; 10,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,27</t>
+          <t>4,62; 11,77</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,79</t>
+          <t>1,8; 4,4</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,84</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,96</t>
+          <t>4,87; 12,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,61</t>
+          <t>4,02; 7,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,84</t>
+          <t>5,33; 14,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,0</t>
+          <t>5,57; 10,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,95</t>
+          <t>3,41; 6,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,99</t>
+          <t>4,41; 6,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,87</t>
+          <t>4,92; 8,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,51; 8,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,92</t>
+          <t>4,36; 7,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,61</t>
+          <t>4,61; 6,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,25</t>
+          <t>5,74; 9,92</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,7</t>
+          <t>5,44; 8,69</t>
         </is>
       </c>
     </row>
